--- a/jira_export_2026-09-30.xlsx
+++ b/jira_export_2026-09-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>52,117 €</t>
+          <t>53,788 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>13,514 €</t>
+          <t>13,654 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>38,602 €</t>
+          <t>40,135 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -4193,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>908.01</v>
+        <v>1077.3</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>165.09</v>
+        <v>195.87</v>
       </c>
     </row>
     <row r="49">
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>26.18</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="53">
@@ -4901,10 +4901,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>51</v>
+        <v>374</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>9.27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59">
@@ -6269,10 +6269,10 @@
         <v>0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>337.5</v>
+        <v>405</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>245.45</v>
+        <v>294.55</v>
       </c>
     </row>
     <row r="78">
@@ -8133,10 +8133,10 @@
         <v>0</v>
       </c>
       <c r="O103" s="13" t="n">
-        <v>130</v>
+        <v>1170</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>26</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104">
@@ -13523,10 +13523,10 @@
         <v>39735.86599999999</v>
       </c>
       <c r="O184" s="19" t="n">
-        <v>52116.67799999999</v>
+        <v>53788.46799999999</v>
       </c>
       <c r="P184" s="19" t="n">
-        <v>168.9</v>
+        <v>174.32</v>
       </c>
     </row>
   </sheetData>
@@ -15146,16 +15146,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>415154</v>
+        <v>413482</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>187883</v>
+        <v>186606</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>227271</v>
+        <v>226876</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>157595</v>
+        <v>157200</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>16523</v>
@@ -15171,16 +15171,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>177341</v>
+        <v>177201</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>51589</v>
+        <v>51521</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>125752</v>
+        <v>125680</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>106357</v>
+        <v>106285</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>9175</v>
@@ -15196,16 +15196,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>237814</v>
+        <v>236281</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>136294</v>
+        <v>135085</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>101520</v>
+        <v>101197</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>51238</v>
+        <v>50915</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>7348</v>

--- a/jira_export_2026-09-30.xlsx
+++ b/jira_export_2026-09-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>53,788 €</t>
+          <t>54,178 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>40,135 €</t>
+          <t>40,525 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>472 h</t>
+          <t>480 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P184"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1066,70 +1066,70 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35840</t>
+          <t>PDMDEP-35962</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SETE] - Publication des actes</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT BRIEUC ] - migration vers GEODP 2 PLACIER avec option ORMC </t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t xml:space="preserve">COMMUNE DE SAINT BRIEUC </t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Abonnement Publication des actes</t>
+          <t xml:space="preserve">migration vers GEODP 2 PLACIER avec option ORMC </t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35902</t>
+          <t>PDMDEP-35969</t>
         </is>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>00182109</t>
+          <t>00182759</t>
         </is>
       </c>
       <c r="N5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="P5" s="13" t="n">
         <v>0</v>
@@ -1138,12 +1138,12 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35767</t>
+          <t>PDMDEP-35840</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)] - MM - Up - LiExp - Formation Admin</t>
+          <t>[COMMUNE DE SETE] - Publication des actes</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Formation Admin</t>
+          <t>Abonnement Publication des actes</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -1178,23 +1178,23 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35771</t>
+          <t>PDMDEP-35902</t>
         </is>
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>00181751</t>
+          <t>00182109</t>
         </is>
       </c>
       <c r="N6" s="16" t="n">
@@ -1210,12 +1210,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35715</t>
+          <t>PDMDEP-35767</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Dunkerque] - Mise à jour cartographique Littéralis Expert </t>
+          <t>[DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)] - MM - Up - LiExp - Formation Admin</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Commune de Dunkerque</t>
+          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise à jour cartographique Littéralis Expert </t>
+          <t>MM - Up - LiExp - Formation Admin</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1250,17 +1250,25 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="J7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="12" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-35771</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>00181751</t>
+        </is>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0</v>
       </c>
@@ -1274,27 +1282,27 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35715</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - 10h de crédits modélisation LITT EXP</t>
+          <t xml:space="preserve">[Commune de Dunkerque] - Mise à jour cartographique Littéralis Expert </t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>10h de crédits modélisation LITT EXP</t>
+          <t xml:space="preserve">Mise à jour cartographique Littéralis Expert </t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -1304,7 +1312,7 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
@@ -1321,18 +1329,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35687</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
-        <is>
-          <t>00181396</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
       <c r="N8" s="16" t="n">
         <v>0</v>
       </c>
@@ -1346,12 +1346,12 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
+          <t>[VILLE DE SURESNES] - 10h de crédits modélisation LITT EXP</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
+          <t>10h de crédits modélisation LITT EXP</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -1386,59 +1386,59 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>4.75</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>638.25</v>
+        <v>0</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>134.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>[Commune de la Roche-sur-Yon] - Audit Littéralis</t>
+          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Audit Littéralis</t>
+          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -1465,37 +1465,37 @@
         <v>0</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.75</v>
+        <v>4.75</v>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>0</v>
+        <v>638.25</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)] - Réinstallation nouveaux serveurs (test et prod)</t>
+          <t>[Commune de la Roche-sur-Yon] - Audit Littéralis</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveaux serveurs (test et prod)</t>
+          <t>Audit Littéralis</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -1530,23 +1530,23 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="N11" s="13" t="n">
@@ -1562,27 +1562,27 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)] - Réinstallation nouveaux serveurs (test et prod)</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>API Publication</t>
+          <t>Réinstallation nouveaux serveurs (test et prod)</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -1609,57 +1609,57 @@
         <v>0</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>4.25</v>
+        <v>1</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="N12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>89.5</v>
+        <v>0</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>21.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PRIVAS] - Migration Placier sans nouveau matériel</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Migration Placier sans nouveau matériel</t>
+          <t>API Publication</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1669,64 +1669,64 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>1.75</v>
+        <v>4.25</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>00180831</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="N13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>145</v>
+        <v>89.5</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>82.86</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[COMMUNE DE PRIVAS] - Migration Placier sans nouveau matériel</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>Migration Placier sans nouveau matériel</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -1746,64 +1746,64 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00180831</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>1257</v>
+        <v>145</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfert de compétence Analyse </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -1825,23 +1825,23 @@
         <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="N15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="P15" s="13" t="n">
         <v>0</v>
@@ -1850,12 +1850,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35445</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOURG EN BRESSE</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">Transfert de compétence Analyse </t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H16" s="15" t="inlineStr">
@@ -1890,17 +1890,25 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L16" s="15" t="inlineStr"/>
-      <c r="M16" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
       <c r="N16" s="16" t="n">
         <v>0</v>
       </c>
@@ -1914,27 +1922,27 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35445</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE BOURG EN BRESSE</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -1944,7 +1952,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -1961,57 +1969,49 @@
         <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-35439</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>00180506</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="13" t="n">
-        <v>1470.38</v>
-      </c>
-      <c r="O17" s="17" t="n">
-        <v>1390.9</v>
+        <v>0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>278.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Saint Cast le Guildo ] - Migration GEODP 2 </t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP 2 </t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -2021,64 +2021,64 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="16" t="n">
-        <v>240</v>
+        <v>1470.38</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>1390.9</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>137.14</v>
+        <v>278.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35343</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT BRIEUC ] - Migration GEODP PLACIER et MODULE ODP </t>
+          <t xml:space="preserve">[Commune de Saint Cast le Guildo ] - Migration GEODP 2 </t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE SAINT BRIEUC </t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP PLACIER et MODULE ODP </t>
+          <t xml:space="preserve">Migration GEODP 2 </t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -2098,33 +2098,33 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35352</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>00179476</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="N19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>510</v>
+        <v>240</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>0</v>
+        <v>137.14</v>
       </c>
     </row>
     <row r="20">
@@ -2766,9 +2766,9 @@
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>709.2</v>
-      </c>
-      <c r="O28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="16" t="n">
         <v>197</v>
       </c>
       <c r="P28" s="16" t="n">
@@ -4457,7 +4457,7 @@
         <v>3</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>144</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>52.36</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="53">
@@ -4957,7 +4957,7 @@
         <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>1242.9</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>261.66</v>
+        <v>216.16</v>
       </c>
     </row>
     <row r="60">
@@ -6973,7 +6973,7 @@
         <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>1122</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>320.57</v>
+        <v>172.62</v>
       </c>
     </row>
     <row r="88">
@@ -11913,7 +11913,7 @@
         <v>21</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>25.83</v>
+        <v>27.83</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -12508,22 +12508,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12541,19 +12541,19 @@
       </c>
       <c r="H167" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12570,12 +12570,12 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12603,19 +12603,19 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -12632,22 +12632,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12670,14 +12670,14 @@
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>3.58</v>
+        <v>1.5</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12694,22 +12694,22 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12722,35 +12722,27 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M170" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12764,22 +12756,22 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E171" s="12" t="n">
@@ -12792,23 +12784,35 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr"/>
-      <c r="M171" s="12" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12822,12 +12826,12 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
@@ -12837,7 +12841,7 @@
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E172" s="15" t="n">
@@ -12853,32 +12857,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H172" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H172" s="15" t="inlineStr"/>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L172" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M172" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L172" s="15" t="inlineStr"/>
+      <c r="M172" s="15" t="inlineStr"/>
       <c r="N172" s="16" t="n">
         <v>0</v>
       </c>
@@ -12892,28 +12884,26 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E173" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v/>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
@@ -12927,22 +12917,30 @@
       </c>
       <c r="H173" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L173" s="12" t="inlineStr"/>
-      <c r="M173" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M173" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N173" s="13" t="n">
         <v>0</v>
       </c>
@@ -12956,23 +12954,27 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C174" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C174" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F174" s="15" t="inlineStr">
@@ -12987,19 +12989,19 @@
       </c>
       <c r="H174" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>7</v>
+        <v>0.25</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -13016,21 +13018,25 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr"/>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E175" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13038,52 +13044,52 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H175" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L175" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
       <c r="N175" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O175" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P175" s="13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr"/>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E176" s="15" t="inlineStr"/>
@@ -13094,7 +13100,7 @@
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr"/>
@@ -13107,35 +13113,39 @@
         <v>2</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L176" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L176" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M176" s="15" t="inlineStr"/>
       <c r="N176" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O176" s="16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P176" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -13152,14 +13162,14 @@
       <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L177" s="12" t="inlineStr"/>
       <c r="M177" s="12" t="inlineStr"/>
@@ -13176,18 +13186,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13198,31 +13208,23 @@
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M178" s="15" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr"/>
+      <c r="M178" s="15" t="inlineStr"/>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
@@ -13236,18 +13238,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13258,23 +13260,31 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr"/>
-      <c r="M179" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N179" s="13" t="n">
         <v>0</v>
       </c>
@@ -13288,18 +13298,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13310,31 +13320,23 @@
       </c>
       <c r="G180" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L180" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M180" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L180" s="15" t="inlineStr"/>
+      <c r="M180" s="15" t="inlineStr"/>
       <c r="N180" s="16" t="n">
         <v>0</v>
       </c>
@@ -13348,18 +13350,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-1158</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PLERIN</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PLERIN</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13370,23 +13372,31 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L181" s="12" t="inlineStr"/>
-      <c r="M181" s="12" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="L181" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M181" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N181" s="13" t="n">
         <v>0</v>
       </c>
@@ -13400,18 +13410,18 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1158</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr"/>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr"/>
@@ -13428,14 +13438,14 @@
       <c r="H182" s="15" t="inlineStr"/>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13452,18 +13462,18 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -13480,11 +13490,11 @@
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K183" s="12" t="n">
         <v>0.25</v>
@@ -13502,31 +13512,83 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="18" t="inlineStr">
+      <c r="A184" s="14" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B184" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C184" s="15" t="inlineStr"/>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E184" s="15" t="inlineStr"/>
+      <c r="F184" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G184" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H184" s="15" t="inlineStr"/>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="J184" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K184" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L184" s="15" t="inlineStr"/>
+      <c r="M184" s="15" t="inlineStr"/>
+      <c r="N184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B184" s="18" t="inlineStr"/>
-      <c r="C184" s="18" t="inlineStr"/>
-      <c r="D184" s="18" t="inlineStr"/>
-      <c r="E184" s="18" t="inlineStr"/>
-      <c r="F184" s="18" t="inlineStr"/>
-      <c r="G184" s="18" t="inlineStr"/>
-      <c r="H184" s="18" t="inlineStr"/>
-      <c r="I184" s="18" t="inlineStr"/>
-      <c r="J184" s="18" t="inlineStr"/>
-      <c r="K184" s="18" t="inlineStr"/>
-      <c r="L184" s="18" t="inlineStr"/>
-      <c r="M184" s="18" t="inlineStr"/>
-      <c r="N184" s="19" t="n">
-        <v>39735.86599999999</v>
-      </c>
-      <c r="O184" s="19" t="n">
-        <v>53788.46799999999</v>
-      </c>
-      <c r="P184" s="19" t="n">
-        <v>174.32</v>
+      <c r="B185" s="18" t="inlineStr"/>
+      <c r="C185" s="18" t="inlineStr"/>
+      <c r="D185" s="18" t="inlineStr"/>
+      <c r="E185" s="18" t="inlineStr"/>
+      <c r="F185" s="18" t="inlineStr"/>
+      <c r="G185" s="18" t="inlineStr"/>
+      <c r="H185" s="18" t="inlineStr"/>
+      <c r="I185" s="18" t="inlineStr"/>
+      <c r="J185" s="18" t="inlineStr"/>
+      <c r="K185" s="18" t="inlineStr"/>
+      <c r="L185" s="18" t="inlineStr"/>
+      <c r="M185" s="18" t="inlineStr"/>
+      <c r="N185" s="19" t="n">
+        <v>37769.666</v>
+      </c>
+      <c r="O185" s="19" t="n">
+        <v>54178.46799999999</v>
+      </c>
+      <c r="P185" s="19" t="n">
+        <v>171.41</v>
       </c>
     </row>
   </sheetData>
@@ -13711,6 +13773,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15000,16 +15063,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>158.92</v>
+        <v>160.42</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>50.67</v>
+        <v>53.67</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>19.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>229.33</v>
+        <v>233.83</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>35.42</v>
@@ -15019,7 +15082,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15093,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>0</v>
@@ -15039,7 +15102,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>77.5</v>
+        <v>80.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>7.5</v>
@@ -15049,7 +15112,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -15061,7 +15124,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>117</v>
+        <v>117.5</v>
       </c>
     </row>
   </sheetData>
@@ -15146,19 +15209,19 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>413482</v>
+        <v>415042</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>186606</v>
+        <v>175576</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>226876</v>
+        <v>239466</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>157200</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>16523</v>
+        <v>29113</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>25847</v>
@@ -15196,19 +15259,19 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>236281</v>
+        <v>237841</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>135085</v>
+        <v>124055</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>101197</v>
+        <v>113787</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>50915</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>7348</v>
+        <v>19938</v>
       </c>
       <c r="G7" s="27" t="n">
         <v>18153</v>
@@ -16014,7 +16077,7 @@
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="21">
@@ -16706,7 +16769,7 @@
         </is>
       </c>
       <c r="I36" s="25" t="n">
-        <v>97451</v>
+        <v>101951</v>
       </c>
     </row>
     <row r="37">
@@ -16748,7 +16811,7 @@
         </is>
       </c>
       <c r="I38" s="25" t="n">
-        <v>71629</v>
+        <v>76129</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-30.xlsx
+++ b/jira_export_2026-09-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>54,178 €</t>
+          <t>57,715 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>13,654 €</t>
+          <t>16,773 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>40,525 €</t>
+          <t>40,943 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>480 h</t>
+          <t>482 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3185,10 +3185,10 @@
         <v>1100</v>
       </c>
       <c r="O34" s="17" t="n">
-        <v>440</v>
+        <v>660</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>880</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="35">
@@ -4457,7 +4457,7 @@
         <v>3</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>144</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>44.31</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="53">
@@ -4754,9 +4754,9 @@
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>1278</v>
-      </c>
-      <c r="O56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>1207</v>
       </c>
       <c r="P56" s="16" t="n">
@@ -5317,7 +5317,7 @@
         <v>3</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>998.25</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>95.06999999999999</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>16</v>
+        <v>304</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>11.64</v>
+        <v>221.09</v>
       </c>
     </row>
     <row r="79">
@@ -6989,10 +6989,10 @@
         <v>0</v>
       </c>
       <c r="O87" s="13" t="n">
-        <v>1122</v>
+        <v>1540</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>172.62</v>
+        <v>236.92</v>
       </c>
     </row>
     <row r="88">
@@ -8405,7 +8405,7 @@
         <v>7</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
@@ -9423,10 +9423,10 @@
         <v>0</v>
       </c>
       <c r="O121" s="13" t="n">
-        <v>0</v>
+        <v>750.7</v>
       </c>
       <c r="P121" s="13" t="n">
-        <v>0</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="122">
@@ -9479,7 +9479,7 @@
         <v>10</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>10</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>10</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="O124" s="16" t="n">
-        <v>0</v>
+        <v>1790</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0</v>
+        <v>701.96</v>
       </c>
     </row>
     <row r="125">
@@ -9695,7 +9695,7 @@
         <v>10</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>10</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
@@ -9852,11 +9852,11 @@
       <c r="N127" s="13" t="n">
         <v>70.2</v>
       </c>
-      <c r="O127" s="17" t="n">
-        <v>0</v>
+      <c r="O127" s="13" t="n">
+        <v>70.2</v>
       </c>
       <c r="P127" s="13" t="n">
-        <v>0</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="128">
@@ -12615,7 +12615,7 @@
         <v>34</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -13582,13 +13582,13 @@
       <c r="L185" s="18" t="inlineStr"/>
       <c r="M185" s="18" t="inlineStr"/>
       <c r="N185" s="19" t="n">
-        <v>37769.666</v>
+        <v>36491.666</v>
       </c>
       <c r="O185" s="19" t="n">
-        <v>54178.46799999999</v>
+        <v>57715.36799999999</v>
       </c>
       <c r="P185" s="19" t="n">
-        <v>171.41</v>
+        <v>181.03</v>
       </c>
     </row>
   </sheetData>
@@ -15063,16 +15063,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>160.42</v>
+        <v>162.92</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>53.67</v>
+        <v>53.92</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>19.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>233.83</v>
+        <v>236.58</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>35.42</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -15209,22 +15209,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>415042</v>
+        <v>411506</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>175576</v>
+        <v>174537</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>239466</v>
+        <v>236968</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>157200</v>
+        <v>154772</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>29113</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>25847</v>
+        <v>25777</v>
       </c>
     </row>
     <row r="6">
@@ -15234,22 +15234,22 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>177201</v>
+        <v>174082</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>51521</v>
+        <v>50483</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>125680</v>
+        <v>123600</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>106285</v>
+        <v>104275</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>9175</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>7695</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="7">
@@ -15259,16 +15259,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>237841</v>
+        <v>237423</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>124055</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>113787</v>
+        <v>113369</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>50915</v>
+        <v>50497</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>19938</v>

--- a/jira_export_2026-09-30.xlsx
+++ b/jira_export_2026-09-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>57,715 €</t>
+          <t>57,875 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>16,773 €</t>
+          <t>16,933 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>482 h</t>
+          <t>483 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -3326,9 +3326,9 @@
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>965.925</v>
-      </c>
-      <c r="O36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="16" t="n">
         <v>643.95</v>
       </c>
       <c r="P36" s="16" t="n">
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>304</v>
+        <v>464</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>221.09</v>
+        <v>337.45</v>
       </c>
     </row>
     <row r="79">
@@ -13582,13 +13582,13 @@
       <c r="L185" s="18" t="inlineStr"/>
       <c r="M185" s="18" t="inlineStr"/>
       <c r="N185" s="19" t="n">
-        <v>36491.666</v>
+        <v>35525.741</v>
       </c>
       <c r="O185" s="19" t="n">
-        <v>57715.36799999999</v>
+        <v>57875.36799999999</v>
       </c>
       <c r="P185" s="19" t="n">
-        <v>181.03</v>
+        <v>181.39</v>
       </c>
     </row>
   </sheetData>
@@ -15069,10 +15069,10 @@
         <v>53.92</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>236.58</v>
+        <v>236.83</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>35.42</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15124,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -15209,10 +15209,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>411506</v>
+        <v>411346</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>174537</v>
+        <v>174377</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>236968</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>174082</v>
+        <v>173922</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>50483</v>
+        <v>50323</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>123600</v>
